--- a/Excel Class Files/Part 7 Data Study.xlsx
+++ b/Excel Class Files/Part 7 Data Study.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A6DBC1-92DC-4078-B635-0B9A567EE52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BBA0A3-F10A-4201-93D7-62CBC27D1F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6369089C-2641-4997-A4E3-DF2B02DD58B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{6369089C-2641-4997-A4E3-DF2B02DD58B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Filter and sorting" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Text-to-Column" sheetId="6" r:id="rId4"/>
     <sheet name="Flash Fill" sheetId="7" r:id="rId5"/>
     <sheet name="Data Validation" sheetId="8" r:id="rId6"/>
-    <sheet name="Name Range" sheetId="9" r:id="rId7"/>
+    <sheet name="Find &amp; Replace" sheetId="10" r:id="rId7"/>
+    <sheet name="Name Range" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="77">
   <si>
     <t>Abhishek Patel</t>
   </si>
@@ -580,22 +581,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -608,14 +598,23 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -969,496 +968,496 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>450</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>7</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6">
         <v>3150</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6">
         <v>1200</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>450</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>7</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>3150</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7">
         <v>1200</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>350</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8">
         <v>1750</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8">
         <v>700</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>700</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>7</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9">
         <v>4900</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9">
         <v>550</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>450</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10">
         <v>1350</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10">
         <v>500</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" t="s">
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11">
         <v>425</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11">
         <v>850</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11">
         <v>450</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12">
         <v>450</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12">
         <v>1800</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12">
         <v>450</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13">
         <v>300</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13">
         <v>300</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13">
         <v>450</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14">
         <v>650</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14">
         <v>2600</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14">
         <v>400</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15">
         <v>700</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15">
         <v>4</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15">
         <v>2800</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15">
         <v>350</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16">
         <v>300</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16">
         <v>1500</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16">
         <v>350</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17">
         <v>500</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17">
         <v>3</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17">
         <v>1500</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17">
         <v>300</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18">
         <v>250</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18">
         <v>2</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18">
         <v>500</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18">
         <v>300</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19">
         <v>500</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19">
         <v>3</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19">
         <v>1500</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19">
         <v>50</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20">
         <v>600</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20">
         <v>5</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20">
         <v>3000</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21">
         <v>350</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21">
         <v>4</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21">
         <v>1400</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21">
         <v>-100</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" t="s">
         <v>1</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22">
         <v>700</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22">
         <v>5</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22">
         <v>3500</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22">
         <v>-100</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23">
         <v>600</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23">
         <v>3</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23">
         <v>1800</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" t="s">
         <v>2</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23">
         <v>-250</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" t="s">
         <v>1</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1489,90 +1488,90 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="7">
         <v>12337</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="5">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="7">
         <v>51041</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="5">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="7">
         <v>69245</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="5">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="7">
         <v>87381</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="5">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="7">
         <v>26966</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="5">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="7">
         <v>55869</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="5">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="7">
         <v>64282</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="5">
         <v>27</v>
       </c>
     </row>
@@ -1590,191 +1589,191 @@
     <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-    </row>
-    <row r="2" spans="1:10" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-    </row>
-    <row r="3" spans="1:10" s="22" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" s="14" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="5">
         <v>101</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="5">
         <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="5">
         <v>102</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="5">
         <v>60000</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="5">
         <v>103</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="5">
         <v>55000</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="5">
         <v>104</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="5">
         <v>60000</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="5">
         <v>105</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="5">
         <v>50000</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="5">
         <v>101</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="5">
         <v>50000</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="5">
         <v>103</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="5">
         <v>55000</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="5">
         <v>106</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="5">
         <v>45000</v>
       </c>
-      <c r="F14" s="16"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="5">
         <v>102</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="5">
         <v>60000</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="10" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1800,92 +1799,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="G6" s="10" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="G6" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="G7" s="10" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="G8" s="10" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1910,92 +1909,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="10"/>
+      <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="10"/>
+      <c r="C10" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2019,6 +2018,510 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CA2376-A840-4352-A551-B8C93EFD74BF}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>450</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>3150</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1200</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>450</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>3150</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>350</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1750</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>700</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>700</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>4900</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>550</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>450</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1350</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>500</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>425</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>850</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>450</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>450</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1800</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>450</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>300</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>300</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>450</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>650</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>2600</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>400</v>
+      </c>
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>700</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>2800</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>350</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>300</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>1500</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>350</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>500</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>1500</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>300</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>250</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>500</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <v>300</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>500</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>1500</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>600</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>3000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>350</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>1400</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>-100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>700</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <v>3500</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>-100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>600</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>1800</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>-250</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992D7068-15B3-4BD1-8FF6-5C3A8A7093D5}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2027,96 +2530,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="7">
         <v>12337</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="5">
         <v>30</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="8">
         <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="7">
         <v>51041</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="5">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="7">
         <v>69245</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="5">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="7">
         <v>87381</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="5">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="7">
         <v>26966</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="5">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="7">
         <v>55869</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="5">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="7">
         <v>64282</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="5">
         <v>27</v>
       </c>
     </row>
